--- a/MCMI-III_Scoring_Tool_V2.xlsx
+++ b/MCMI-III_Scoring_Tool_V2.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,7 +124,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -143,8 +143,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,19 +549,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
     <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
@@ -756,44 +754,44 @@
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>X_Raw_D</t>
+          <t>D_Raw</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>Adj_18B</t>
+          <t>D_18B</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>Adj_SPP</t>
+          <t>D_SPP</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>AD_Val</t>
+          <t>AD_v</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>Adj_2AS</t>
+          <t>AD_2AS</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>AD_Val2</t>
+          <t>AD_v2</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>Adj_2B8BC</t>
+          <t>AD_2B8B</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Enter 1=TRUE or 0=FALSE for each item. Scoring is automatic.</t>
+          <t>Enter 1=TRUE or 0=FALSE for each item. All scoring is automatic.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1146,13 +1144,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Inpatient (Y/N):</t>
+          <t>Inpatient(Y/N):</t>
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Axis I weeks:</t>
+          <t>Axis I wks:</t>
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
@@ -1384,7 +1382,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ITEM RESPONSES</t>
+          <t>ITEM RESPONSES (Enter 1=True, 0=False)</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -5317,87 +5315,6 @@
         <v>169</v>
       </c>
       <c r="N37" s="7" t="n"/>
-      <c r="P37" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>115</v>
-      </c>
-      <c r="R37" t="n">
-        <v>115</v>
-      </c>
-      <c r="S37" t="n">
-        <v>115</v>
-      </c>
-      <c r="T37" t="n">
-        <v>115</v>
-      </c>
-      <c r="U37" t="n">
-        <v>88</v>
-      </c>
-      <c r="V37" t="n">
-        <v>115</v>
-      </c>
-      <c r="W37" t="n">
-        <v>115</v>
-      </c>
-      <c r="X37" t="n">
-        <v>115</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>115</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>100</v>
-      </c>
       <c r="AR37" t="n">
         <v>69</v>
       </c>
@@ -5752,7 +5669,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>SCORING RESULTS</t>
+          <t>SCORING TABLE</t>
         </is>
       </c>
       <c r="AR45" t="n">
@@ -5783,7 +5700,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Scale</t>
@@ -5801,49 +5718,42 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Raw
-Score</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>BR Score
-(auto)</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Disc
-Adj</t>
+          <t>Disc</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>A/D
-Adj</t>
+          <t>A/D</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Inp
-Adj</t>
+          <t>Inp</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Den/
-Comp</t>
+          <t>Den</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>FINAL
-BR</t>
+          <t>FINAL BR</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>Signif.</t>
+          <t>Signif</t>
         </is>
       </c>
       <c r="AR46" t="n">
@@ -5967,7 +5877,7 @@
         <v/>
       </c>
       <c r="E48" s="12">
-        <f>VLOOKUP(MIN(D48,35),$P:$AO,COLUMN($AO$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D48,34),$P:$AO,COLUMN($AO$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F48" s="13" t="n">
@@ -6039,7 +5949,7 @@
         <v/>
       </c>
       <c r="E49" s="12">
-        <f>VLOOKUP(MIN(D49,35),$P:$AP,COLUMN($AP$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D49,34),$P:$AP,COLUMN($AP$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F49" s="13" t="n">
@@ -6111,11 +6021,11 @@
         <v/>
       </c>
       <c r="E50" s="12">
-        <f>VLOOKUP(MIN(D50,35),$P:$Q,COLUMN($Q$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D50,34),$P:$Q,COLUMN($Q$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F50" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G50" s="13" t="n">
@@ -6184,11 +6094,11 @@
         <v/>
       </c>
       <c r="E51" s="12">
-        <f>VLOOKUP(MIN(D51,35),$P:$R,COLUMN($R$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D51,34),$P:$R,COLUMN($R$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F51" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G51" s="6">
@@ -6258,11 +6168,11 @@
         <v/>
       </c>
       <c r="E52" s="12">
-        <f>VLOOKUP(MIN(D52,35),$P:$S,COLUMN($S$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D52,34),$P:$S,COLUMN($S$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F52" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G52" s="6">
@@ -6332,11 +6242,11 @@
         <v/>
       </c>
       <c r="E53" s="12">
-        <f>VLOOKUP(MIN(D53,35),$P:$T,COLUMN($T$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D53,34),$P:$T,COLUMN($T$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F53" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G53" s="13" t="n">
@@ -6405,11 +6315,11 @@
         <v/>
       </c>
       <c r="E54" s="12">
-        <f>VLOOKUP(MIN(D54,35),$P:$U,COLUMN($U$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D54,34),$P:$U,COLUMN($U$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F54" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G54" s="13" t="n">
@@ -6478,11 +6388,11 @@
         <v/>
       </c>
       <c r="E55" s="12">
-        <f>VLOOKUP(MIN(D55,35),$P:$V,COLUMN($V$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D55,34),$P:$V,COLUMN($V$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F55" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G55" s="13" t="n">
@@ -6551,11 +6461,11 @@
         <v/>
       </c>
       <c r="E56" s="12">
-        <f>VLOOKUP(MIN(D56,35),$P:$W,COLUMN($W$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D56,34),$P:$W,COLUMN($W$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F56" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G56" s="13" t="n">
@@ -6624,11 +6534,11 @@
         <v/>
       </c>
       <c r="E57" s="12">
-        <f>VLOOKUP(MIN(D57,35),$P:$X,COLUMN($X$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D57,34),$P:$X,COLUMN($X$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F57" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G57" s="13" t="n">
@@ -6697,11 +6607,11 @@
         <v/>
       </c>
       <c r="E58" s="12">
-        <f>VLOOKUP(MIN(D58,35),$P:$Y,COLUMN($Y$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D58,34),$P:$Y,COLUMN($Y$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F58" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G58" s="13" t="n">
@@ -6770,11 +6680,11 @@
         <v/>
       </c>
       <c r="E59" s="12">
-        <f>VLOOKUP(MIN(D59,35),$P:$Z,COLUMN($Z$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D59,34),$P:$Z,COLUMN($Z$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F59" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G59" s="13" t="n">
@@ -6843,11 +6753,11 @@
         <v/>
       </c>
       <c r="E60" s="12">
-        <f>VLOOKUP(MIN(D60,35),$P:$AA,COLUMN($AA$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D60,34),$P:$AA,COLUMN($AA$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F60" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AV,2,TRUE)</f>
         <v/>
       </c>
       <c r="G60" s="6">
@@ -6917,11 +6827,11 @@
         <v/>
       </c>
       <c r="E61" s="12">
-        <f>VLOOKUP(MIN(D61,35),$P:$AB,COLUMN($AB$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D61,34),$P:$AB,COLUMN($AB$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F61" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G61" s="6">
@@ -6991,11 +6901,11 @@
         <v/>
       </c>
       <c r="E62" s="12">
-        <f>VLOOKUP(MIN(D62,35),$P:$AC,COLUMN($AC$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D62,34),$P:$AC,COLUMN($AC$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F62" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G62" s="6">
@@ -7065,11 +6975,11 @@
         <v/>
       </c>
       <c r="E63" s="12">
-        <f>VLOOKUP(MIN(D63,35),$P:$AD,COLUMN($AD$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D63,34),$P:$AD,COLUMN($AD$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F63" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G63" s="13" t="n">
@@ -7130,7 +7040,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D64" s="11">
@@ -7138,11 +7048,11 @@
         <v/>
       </c>
       <c r="E64" s="12">
-        <f>VLOOKUP(MIN(D64,35),$P:$AE,COLUMN($AE$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D64,34),$P:$AE,COLUMN($AE$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F64" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G64" s="13" t="n">
@@ -7203,7 +7113,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D65" s="11">
@@ -7211,11 +7121,11 @@
         <v/>
       </c>
       <c r="E65" s="12">
-        <f>VLOOKUP(MIN(D65,35),$P:$AF,COLUMN($AF$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D65,34),$P:$AF,COLUMN($AF$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F65" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G65" s="13" t="n">
@@ -7276,7 +7186,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D66" s="11">
@@ -7284,11 +7194,11 @@
         <v/>
       </c>
       <c r="E66" s="12">
-        <f>VLOOKUP(MIN(D66,35),$P:$AG,COLUMN($AG$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D66,34),$P:$AG,COLUMN($AG$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F66" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G66" s="13" t="n">
@@ -7349,7 +7259,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D67" s="11">
@@ -7357,11 +7267,11 @@
         <v/>
       </c>
       <c r="E67" s="12">
-        <f>VLOOKUP(MIN(D67,35),$P:$AH,COLUMN($AH$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D67,34),$P:$AH,COLUMN($AH$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F67" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G67" s="13" t="n">
@@ -7422,19 +7332,19 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D68" s="11">
-        <f>2*$E$25+2*$H$15+2*$H$38+2*$K$34+2*$N$20+$B$22+$E$14+$E$37+$H$31+$H$39+$K$16+$K$25+$K$42+$N$34+(1-$B$31)</f>
+        <f>2*$E$25+2*$H$15+2*$H$38+2*$K$34+2*$N$20+$B$22+$E$14+$E$37+$H$31+$H$39+$K$16+$K$25+$K$42+$N$34+2*(1-$B$31)</f>
         <v/>
       </c>
       <c r="E68" s="12">
-        <f>VLOOKUP(MIN(D68,35),$P:$AI,COLUMN($AI$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D68,34),$P:$AI,COLUMN($AI$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F68" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G68" s="13" t="n">
@@ -7495,7 +7405,7 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D69" s="11">
@@ -7503,11 +7413,11 @@
         <v/>
       </c>
       <c r="E69" s="12">
-        <f>VLOOKUP(MIN(D69,35),$P:$AJ,COLUMN($AJ$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D69,34),$P:$AJ,COLUMN($AJ$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F69" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G69" s="13" t="n">
@@ -7568,7 +7478,7 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Clinical Syn</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="D70" s="11">
@@ -7576,11 +7486,11 @@
         <v/>
       </c>
       <c r="E70" s="12">
-        <f>VLOOKUP(MIN(D70,35),$P:$AK,COLUMN($AK$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D70,34),$P:$AK,COLUMN($AK$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F70" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G70" s="13" t="n">
@@ -7636,7 +7546,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Thought Dis</t>
+          <t>Thought Disorder</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -7649,11 +7559,11 @@
         <v/>
       </c>
       <c r="E71" s="12">
-        <f>VLOOKUP(MIN(D71,35),$P:$AL,COLUMN($AL$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D71,34),$P:$AL,COLUMN($AL$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F71" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G71" s="13" t="n">
@@ -7710,7 +7620,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Major Dep</t>
+          <t>Major Depression</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7723,11 +7633,11 @@
         <v/>
       </c>
       <c r="E72" s="12">
-        <f>VLOOKUP(MIN(D72,35),$P:$AM,COLUMN($AM$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D72,34),$P:$AM,COLUMN($AM$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F72" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G72" s="13" t="n">
@@ -7784,7 +7694,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Delusional</t>
+          <t>Delusional Dis</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7797,11 +7707,11 @@
         <v/>
       </c>
       <c r="E73" s="12">
-        <f>VLOOKUP(MIN(D73,35),$P:$AN,COLUMN($AN$1)-COLUMN($P$1)+1,TRUE)</f>
+        <f>VLOOKUP(MIN(D73,34),$P:$AN,COLUMN($AN$1)-COLUMN($P$1)+1,TRUE)</f>
         <v/>
       </c>
       <c r="F73" s="6">
-        <f>IF(D47="",0,VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE))</f>
+        <f>VLOOKUP(MIN(MAX(D47,0),199),$AU:$AW,3,TRUE)</f>
         <v/>
       </c>
       <c r="G73" s="13" t="n">
@@ -8065,9 +7975,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>INTERPRETATION</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BR 85-115 = PATHOLOGICAL | 75-84 = PRESENT | 60-74 = Suggestive | 0-59 = Normal</t>
         </is>
       </c>
       <c r="AR80" t="n">
@@ -8099,11 +8009,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BR 85-115 = PATHOLOGICAL (Disorder present)</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
       <c r="AR81" t="n">
         <v>113</v>
       </c>
@@ -8133,9 +8039,9 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BR 75-84 = PRESENT (Clinically significant trait)</t>
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>HOW TO USE:</t>
         </is>
       </c>
       <c r="AR82" t="n">
@@ -8169,7 +8075,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BR 60-74 = Suggestive (Subclinical)</t>
+          <t>1. Enter 1 (TRUE) or 0 (FALSE) for all 175 items in yellow cells</t>
         </is>
       </c>
       <c r="AR83" t="n">
@@ -8191,7 +8097,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BR 0-59 = Normal</t>
+          <t>2. Raw scores auto-calculate (proto*2 + nonproto*1 + false*1)</t>
         </is>
       </c>
       <c r="AR84" t="n">
@@ -8211,6 +8117,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3. BR scores auto-calculate from Appendix C tables</t>
+        </is>
+      </c>
       <c r="AR85" t="n">
         <v>117</v>
       </c>
@@ -8228,9 +8139,9 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>INSTRUCTIONS</t>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4. Adjustments (Disc, A/D, Inpatient) are automatic</t>
         </is>
       </c>
       <c r="AR86" t="n">
@@ -8252,7 +8163,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1. Enter 1 (TRUE) or 0 (FALSE) for all 175 items in yellow cells above</t>
+          <t>5. For Denial/Complaint: enter 8 in col I if highest 1-8B is scale 4, 5, or 7</t>
         </is>
       </c>
       <c r="AR87" t="n">
@@ -8274,7 +8185,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2. Raw scores auto-calculate with correct WEIGHTS (proto=2, nonproto=1, false=1)</t>
+          <t>6. Final BR and significance auto-calculate</t>
         </is>
       </c>
       <c r="AR88" t="n">
@@ -8294,11 +8205,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>3. BR scores auto-calculate from Appendix C lookup tables</t>
-        </is>
-      </c>
       <c r="AR89" t="n">
         <v>121</v>
       </c>
@@ -8316,11 +8222,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>4. Disclosure, A/D, and Inpatient adjustments are automatic</t>
-        </is>
-      </c>
       <c r="AR90" t="n">
         <v>122</v>
       </c>
@@ -8338,11 +8239,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>5. For Denial/Complaint (Col I): enter 8 if highest 1-8B scale is 4, 5, or 7</t>
-        </is>
-      </c>
       <c r="AR91" t="n">
         <v>123</v>
       </c>
@@ -8360,11 +8256,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>6. Final BR and Significance appear automatically</t>
-        </is>
-      </c>
       <c r="AR92" t="n">
         <v>124</v>
       </c>
@@ -8382,11 +8273,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>7. Scale 5 (Narcissistic) does NOT multiply by 2/3 - it has 24 items with weights</t>
-        </is>
-      </c>
       <c r="AR93" t="n">
         <v>125</v>
       </c>
@@ -8404,11 +8290,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>8. Validity: V&gt;1 or X&lt;34 or X&gt;178 = INVALID protocol</t>
-        </is>
-      </c>
       <c r="AR94" t="n">
         <v>126</v>
       </c>

--- a/MCMI-III_Scoring_Tool_V2.xlsx
+++ b/MCMI-III_Scoring_Tool_V2.xlsx
@@ -143,7 +143,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -791,7 +791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Enter 1=TRUE or 0=FALSE for each item. All scoring is automatic.</t>
+          <t>Enter 1=TRUE or 0=FALSE. All scoring automatic.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1382,7 +1382,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ITEM RESPONSES (Enter 1=True, 0=False)</t>
+          <t>ITEM RESPONSES (1=True, 0=False)</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="D54" s="11">
-        <f>2*$B$20+2*$B$29+2*$B$40+2*$E$24+2*$E$30+2*$H$18+2*$H$26+$B$18+$B$32+$B$35+$E$21+$E$42+$H$30+$H$37+$K$26+$K$30+$N$42</f>
+        <f>2*$B$20+2*$B$29+2*$B$40+2*$E$24+2*$E$30+2*$H$18+2*$H$26+(1-$B$18)+(1-$B$32)+(1-$B$35)+(1-$E$21)+(1-$E$42)+(1-$H$30)+(1-$H$37)+(1-$K$26)+(1-$K$30)+(1-$N$42)</f>
         <v/>
       </c>
       <c r="E54" s="12">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Thought Disorder</t>
+          <t>Thought Dis</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Major Depression</t>
+          <t>Major Dep</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Delusional Dis</t>
+          <t>Delusional</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B78" s="17">
-        <f>IF(OR(B76&gt;1,B77&lt;34,B77&gt;178),"INVALID PROTOCOL","VALID")</f>
+        <f>IF(OR(B76&gt;1,B77&lt;34,B77&gt;178),"INVALID","VALID")</f>
         <v/>
       </c>
       <c r="AR78" t="n">
@@ -7977,7 +7977,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BR 85-115 = PATHOLOGICAL | 75-84 = PRESENT | 60-74 = Suggestive | 0-59 = Normal</t>
+          <t>BR: 85-115=PATHOLOGICAL | 75-84=PRESENT | 60-74=Suggestive | 0-59=Normal</t>
         </is>
       </c>
       <c r="AR80" t="n">
@@ -8009,7 +8009,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="AR81" t="n">
         <v>113</v>
       </c>
@@ -8075,7 +8074,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1. Enter 1 (TRUE) or 0 (FALSE) for all 175 items in yellow cells</t>
+          <t>1. Enter 1(TRUE) or 0(FALSE) for all 175 items</t>
         </is>
       </c>
       <c r="AR83" t="n">
@@ -8097,7 +8096,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2. Raw scores auto-calculate (proto*2 + nonproto*1 + false*1)</t>
+          <t>2. Raw + BR scores calculate automatically</t>
         </is>
       </c>
       <c r="AR84" t="n">
@@ -8119,7 +8118,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3. BR scores auto-calculate from Appendix C tables</t>
+          <t>3. Adjustments auto-calculate</t>
         </is>
       </c>
       <c r="AR85" t="n">
@@ -8141,7 +8140,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4. Adjustments (Disc, A/D, Inpatient) are automatic</t>
+          <t>4. Only manual step: Col I Denial/Complaint (enter 8 if highest 1-8B is 4,5,7)</t>
         </is>
       </c>
       <c r="AR86" t="n">
@@ -8161,11 +8160,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>5. For Denial/Complaint: enter 8 in col I if highest 1-8B is scale 4, 5, or 7</t>
-        </is>
-      </c>
       <c r="AR87" t="n">
         <v>119</v>
       </c>
@@ -8183,11 +8177,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>6. Final BR and significance auto-calculate</t>
-        </is>
-      </c>
       <c r="AR88" t="n">
         <v>120</v>
       </c>

--- a/MCMI-III_Scoring_Tool_V2.xlsx
+++ b/MCMI-III_Scoring_Tool_V2.xlsx
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="D47" s="11">
-        <f>$B$9+$B$10+$B$11+$B$12+$B$13+$B$14+$B$15+$B$16+$B$17+$B$18+$B$19+$B$20+$B$21+$B$22+$B$23+$B$24+$B$25+$B$26+$B$27+$B$28+$B$29+$B$30+$B$31+$B$32+$B$33+$B$34+$B$35+$B$36+$B$37+$B$38+$B$39+$B$40+$B$41+$B$42+$B$43+$E$9+$E$10+$E$11+$E$12+$E$13+$E$14+$E$15+$E$16+$E$17+$E$18+$E$19+$E$20+$E$21+$E$22+$E$23+$E$24+$E$25+$E$26+$E$27+$E$28+$E$29+$E$30+$E$31+$E$32+$E$33+$E$34+$E$35+$E$36+$E$37+$E$38+$E$39+$E$40+$E$41+$E$42+$E$43+$H$9+$H$10+$H$11+$H$12+$H$13+$H$14+$H$15+$H$16+$H$17+$H$18+$H$19+$H$20+$H$21+$H$22+$H$23+$H$24+$H$25+$H$26+$H$27+$H$28+$H$29+$H$30+$H$31+$H$32+$H$33+$H$34+$H$35+$H$36+$H$37+$H$38+$H$39+$H$40+$H$41+$H$42+$H$43+$K$9+$K$10+$K$11+$K$12+$K$13+$K$14+$K$15+$K$16+$K$17+$K$18+$K$19+$K$20+$K$21+$K$22+$K$23+$K$24+$K$25+$K$26+$K$27+$K$28+$K$29+$K$30+$K$31+$K$32+$K$33+$K$34+$K$35+$K$36+$K$37+$K$38+$K$39+$K$40+$K$41+$K$42+$K$43+$N$9+$N$10+$N$11+$N$12+$N$13+$N$14+$N$15+$N$16+$N$17+$N$18+$N$19+$N$20+$N$21+$N$22+$N$23+$N$24+$N$25+$N$26+$N$27+$N$28+$N$29+$N$30+$N$31+$N$32+$N$33+$N$34+$N$35+$N$36+$N$37+$N$38+$N$39+$N$40+$N$41+$N$42+$N$43</f>
+        <f>D50+D51+D52+D53+D54+D56+D57+D58+D59+D60+ROUND(D55*2/3,0)</f>
         <v/>
       </c>
       <c r="E47" s="12">
@@ -7975,9 +7975,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BR: 85-115=PATHOLOGICAL | 75-84=PRESENT | 60-74=Suggestive | 0-59=Normal</t>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>W INCONSISTENCY</t>
         </is>
       </c>
       <c r="AR80" t="n">
@@ -8009,6 +8009,19 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>W Score:</t>
+        </is>
+      </c>
+      <c r="B81" s="15">
+        <f>IF(AND($B$9=1,$B$12=0),1,0)+IF(AND($B$9=0,$B$12=1),1,0)+IF(AND($B$16=0,$N$9=1),1,0)+IF(AND($B$21=1,$E$39=0),1,0)+IF(AND($B$21=0,$E$39=1),1,0)+IF(AND($B$23=1,$K$36=0),1,0)+IF(AND($B$28=1,$K$15=0),1,0)+IF(AND($B$28=0,$K$15=1),1,0)+IF(AND($B$30=1,$H$21=0),1,0)+IF(AND($B$32=0,$N$19=1),1,0)+IF(AND($B$33=1,$E$29=0),1,0)+IF(AND($B$33=0,$E$29=1),1,0)+IF(AND($B$35=0,$H$30=1),1,0)+IF(AND($B$40=1,$H$18=0),1,0)+IF(AND($B$43=1,$H$22=0),1,0)+IF(AND($B$43=0,$H$22=1),1,0)+IF(AND($E$12=1,$K$21=0),1,0)+IF(AND($E$12=0,$K$21=1),1,0)+IF(AND($E$14=0,$N$34=1),1,0)+IF(AND($E$17=1,$H$24=0),1,0)+IF(AND($E$17=0,$N$18=1),1,0)+IF(AND($E$21=1,$H$30=0),1,0)+IF(AND($E$22=1,$N$14=0),1,0)+IF(AND($E$25=0,$N$20=1),1,0)+IF(AND($E$28=0,$K$33=1),1,0)+IF(AND($E$30=0,$H$18=1),1,0)+IF(AND($E$34=0,$H$14=1),1,0)+IF(AND($E$35=0,$H$24=1),1,0)+IF(AND($E$41=0,$N$30=1),1,0)+IF(AND($E$42=1,$H$37=0),1,0)+IF(AND($E$43=0,$H$42=1),1,0)+IF(AND($H$10=0,$N$10=1),1,0)+IF(AND($H$12=0,$K$10=1),1,0)+IF(AND($H$15=1,$K$34=0),1,0)+IF(AND($H$29=1,$K$39=0),1,0)+IF(AND($H$29=0,$K$39=1),1,0)+IF(AND($K$11=1,$K$38=0),1,0)+IF(AND($K$12=0,$N$32=1),1,0)+IF(AND($K$26=0,$K$31=1),1,0)+IF(AND($K$32=1,$N$41=0),1,0)+IF(AND($K$36=1,$N$13=0),1,0)+IF(AND($N$15=0,$N$17=1),1,0)+IF(AND($N$28=1,$N$32=0),1,0)+IF(AND($N$28=0,$N$41=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>IF(B81&gt;12,"INVALID (random?)",IF(B81&gt;8,"CAUTION","OK"))</f>
+        <v/>
+      </c>
       <c r="AR81" t="n">
         <v>113</v>
       </c>
@@ -8038,11 +8051,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
       <c r="AR82" t="n">
         <v>114</v>
       </c>
@@ -8074,7 +8082,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1. Enter 1(TRUE) or 0(FALSE) for all 175 items</t>
+          <t>BR: 85-115=PATHOLOGICAL | 75-84=PRESENT | 60-74=Suggestive | 0-59=Normal</t>
         </is>
       </c>
       <c r="AR83" t="n">
@@ -8094,11 +8102,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2. Raw + BR scores calculate automatically</t>
-        </is>
-      </c>
       <c r="AR84" t="n">
         <v>116</v>
       </c>
@@ -8116,9 +8119,9 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>3. Adjustments auto-calculate</t>
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>HOW TO USE:</t>
         </is>
       </c>
       <c r="AR85" t="n">
@@ -8140,7 +8143,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4. Only manual step: Col I Denial/Complaint (enter 8 if highest 1-8B is 4,5,7)</t>
+          <t>1. Enter 1(TRUE) or 0(FALSE) for all 175 items</t>
         </is>
       </c>
       <c r="AR86" t="n">
@@ -8160,6 +8163,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2. Raw + BR scores calculate automatically</t>
+        </is>
+      </c>
       <c r="AR87" t="n">
         <v>119</v>
       </c>
@@ -8177,6 +8185,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3. Adjustments auto-calculate</t>
+        </is>
+      </c>
       <c r="AR88" t="n">
         <v>120</v>
       </c>
@@ -8194,6 +8207,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4. Only manual step: Col I Denial/Complaint (enter 8 if highest 1-8B is 4,5,7)</t>
+        </is>
+      </c>
       <c r="AR89" t="n">
         <v>121</v>
       </c>
